--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:28</t>
+    <t xml:space="preserve">2026-09-09 20:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:28</t>
+    <t xml:space="preserve">2026-09-18 10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
